--- a/output/pdf_financials_xlsx/SBMI.xlsx
+++ b/output/pdf_financials_xlsx/SBMI.xlsx
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.890441</v>
+        <v>-1.890441</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>6.072281</v>
+        <v>-6.072281</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.890441</v>
+        <v>-1.890441</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>6.072281</v>
+        <v>-6.072281</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.890441</v>
+        <v>-1.890441</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>6.072281</v>
+        <v>-6.072281</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-2.775747</v>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-31.50735</v>
+        <v>31.50735</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-55.202555</v>
+        <v>55.202555</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.890441</v>
+        <v>-1.890441</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>6.072281</v>
+        <v>-6.072281</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.890441</v>
+        <v>-1.890441</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>6.119281</v>
+        <v>-6.025281</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" s="5" t="n">
-        <v>1.890441</v>
+        <v>-1.890441</v>
       </c>
       <c r="F104" s="5" t="n">
         <v>6.072281</v>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" s="5" t="n">
-        <v>1.890441</v>
+        <v>-1.890441</v>
       </c>
       <c r="F106" s="5" t="n">
         <v>6.073382</v>

--- a/output/pdf_financials_xlsx/SBMI.xlsx
+++ b/output/pdf_financials_xlsx/SBMI.xlsx
@@ -2995,19 +2995,19 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.421127</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.029303</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.068713</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.095647</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.128336</v>
       </c>
     </row>
     <row r="111">
@@ -6171,7 +6171,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>0.421127</v>
       </c>
